--- a/DateBase/orders/Dang Nguyen48_2026-4-6.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-4-6.xlsx
@@ -605,6 +605,9 @@
       <c r="C21" t="str">
         <v>439_九星叶_undefined_undefined_1bunch</v>
       </c>
+      <c r="F21" t="str">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -663,7 +666,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0510591081055105101010551010100</v>
+        <v>05105910810551051010105510101015</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-4-6.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-4-6.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -609,9 +609,343 @@
         <v>15</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>3</v>
+      </c>
+      <c r="C22" t="str">
+        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>761_芍药奶油碗_undefined_undefined_10stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>757_芍药老忠诚_Old Faith_undefined_10stems</v>
+      </c>
+      <c r="F24" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>760_芍药蓝富士_undefined_undefined_10stems</v>
+      </c>
+      <c r="F25" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>458_蓝盆花白色_Scabiosa caucasica white_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>552_蓝盆花紫色_Scabiosa caucasica purple_undefined_1bunch</v>
+      </c>
+      <c r="F27" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>846_玛格丽特_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F28" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>4</v>
+      </c>
+      <c r="C29" t="str">
+        <v>547_粉菠萝_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F29" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>547_粉菠萝_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F30" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>453_国产菠萝_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F31" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>572_乒乓菊白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F32" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>734_乒乓菊红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F33" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>394_矢车菊_Cornflower_undefined_1bunch</v>
+      </c>
+      <c r="F34" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>645_蛇目菊_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F35" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>769_菟葵绿铃铛_undefined_undefined_undefinedundefined</v>
+      </c>
+      <c r="F36" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>5</v>
+      </c>
+      <c r="C37" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F37" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>260_凯拉_Kayla_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F38" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="str">
+        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F39" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="str">
+        <v>478_绿芯向日葵_sunflower mini_undefined_1bunch</v>
+      </c>
+      <c r="F40" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>1_白洋桔梗_White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F41" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>9_茶色洋桔梗_Tea Color Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F42" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F43" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F44" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
+      </c>
+      <c r="F45" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>6</v>
+      </c>
+      <c r="C46" t="str">
+        <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
+      </c>
+      <c r="F46" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="str">
+        <v>606_康乃馨橙光_orange_undefined_20stems</v>
+      </c>
+      <c r="F47" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="str">
+        <v>602_康乃馨白_white_undefined_20stems</v>
+      </c>
+      <c r="F48" t="str">
+        <v>00</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="str">
+        <v>630_吸色康乃馨天蓝_tinted tiffany blue_undefined_20stems</v>
+      </c>
+      <c r="F49" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" xml:space="preserve">
+      <c r="C50" t="str" xml:space="preserve">
+        <v xml:space="preserve">510_翠珠白_Didiscus caeruleus 
+white_Trachymene Coerulea_1bunch</v>
+      </c>
+      <c r="F50" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" xml:space="preserve">
+      <c r="C51" t="str" xml:space="preserve">
+        <v xml:space="preserve">509_翠珠粉_Didiscus caeruleus
+pink_Trachymene Coerulea_1bunch</v>
+      </c>
+      <c r="F51" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" xml:space="preserve">
+      <c r="C52" t="str" xml:space="preserve">
+        <v xml:space="preserve">416_翠珠紫_Didiscus caeruleus
+blue_Trachymene Coerulea_1bunch</v>
+      </c>
+      <c r="F52" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" xml:space="preserve">
+      <c r="C53" t="str" xml:space="preserve">
+        <v xml:space="preserve">508_风铃花白色_Canterbury Bells 
+white_undefined_1bunch</v>
+      </c>
+      <c r="F53" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" xml:space="preserve">
+      <c r="C54" t="str" xml:space="preserve">
+        <v xml:space="preserve">414_风铃花粉色_Canterbury Bells
+pink_undefined_1bunch</v>
+      </c>
+      <c r="F54" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="str">
+        <v>70_朝霞mini_undefined_Gerbera L._20stems</v>
+      </c>
+      <c r="F55" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" t="str">
+        <v>41_拉丝白_Spider White_Gerbera L._20stems</v>
+      </c>
+      <c r="F56" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" t="str">
+        <v>49_亚丁_Pasta Rosata_Gerbera L._10stems</v>
+      </c>
+      <c r="F57" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" t="str">
+        <v>84_堪培拉_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F58" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" t="str">
+        <v>77_珍爱mini_undefined_Gerbera L._20stems</v>
+      </c>
+      <c r="F59" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" t="str">
+        <v>80_冰清玉洁_undefined_Gerbera L._20stems</v>
+      </c>
+      <c r="F60" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="str">
+        <v>47_拉丝玫红_Spider Dark Pink_Gerbera L._20stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L61"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -666,7 +1000,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>05105910810551051010105510101015</v>
+        <v>051059108105510510101055101010158080153010105531010510558755105105201550010201010105101055560</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-4-6.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-4-6.xlsx
@@ -942,6 +942,9 @@
       <c r="C61" t="str">
         <v>47_拉丝玫红_Spider Dark Pink_Gerbera L._20stems</v>
       </c>
+      <c r="F61" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -1000,7 +1003,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>051059108105510510101055101010158080153010105531010510558755105105201550010201010105101055560</v>
+        <v>051059108105510510101055101010158080153010105531010510558755105105201550010201010105101055565</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-4-6.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-4-6.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L69"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -946,9 +946,82 @@
         <v>5</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>7</v>
+      </c>
+      <c r="C62" t="str">
+        <v>418_松虫草白_scabiosa white_undefined_1bunch</v>
+      </c>
+      <c r="F62" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="C63" t="str">
+        <v>421_松虫草黑色_scabiosa black_undefined_1bunch</v>
+      </c>
+      <c r="F63" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="C64" t="str">
+        <v>419_松虫草红_scabiosa watermelon_undefined_1bunch</v>
+      </c>
+      <c r="F64" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="C65" t="str">
+        <v>503_丁香花 粉_lilac pink_undefined_1bunch</v>
+      </c>
+      <c r="F65" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="C66" t="str">
+        <v>410_丁香花 白_lilac white_undefined_1bunch</v>
+      </c>
+      <c r="F66" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>8</v>
+      </c>
+      <c r="C67" t="str">
+        <v>745_海芋红_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F67" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>9</v>
+      </c>
+      <c r="C68" t="str">
+        <v>775_海芋黑_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F68" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="C69" t="str">
+        <v>759_芍药红富士_Kansas_undefined_10stems</v>
+      </c>
+      <c r="F69" t="str">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L69"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1003,7 +1076,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>051059108105510510101055101010158080153010105531010510558755105105201550010201010105101055565</v>
+        <v>0510591081055105101010551010101580801530101055310105105587551051052015500102010101051010555651010151055350</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-4-6.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-4-6.xlsx
@@ -1078,6 +1078,9 @@
       <c r="G2" t="str">
         <v>0510591081055105101010551010101580801530101055310105105587551051052015500102010101051010555651010151055350</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
